--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8297B7CD-9CBB-4514-986A-CEF55AD5678A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B605A6-63D0-4CBF-8E28-E9C155AFF9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,21 @@
     <sheet name="existing" sheetId="1" r:id="rId1"/>
     <sheet name="new" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -522,16 +533,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -548,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -568,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -582,16 +593,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -608,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -628,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -648,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -668,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -688,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -708,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -728,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -748,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -768,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -788,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -808,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -822,13 +833,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -848,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -868,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -888,7 +899,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -908,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -928,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -948,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -968,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -988,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1008,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1028,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1048,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1068,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1088,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1108,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1128,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1148,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1168,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1188,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1208,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1228,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1248,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1268,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1288,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1308,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1328,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B605A6-63D0-4CBF-8E28-E9C155AFF9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C365DB93-DF27-499D-8C0D-CDA9EB9E9A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -1333,7 +1333,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1409,10 +1409,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1429,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1449,10 +1449,10 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1469,10 +1469,10 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1489,10 +1489,10 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1509,10 +1509,10 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1529,10 +1529,10 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1549,10 +1549,10 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1569,10 +1569,10 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1589,10 +1589,10 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1609,10 +1609,10 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1649,10 +1649,10 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1669,10 +1669,10 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1689,10 +1689,10 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1709,10 +1709,10 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1749,10 +1749,10 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1769,10 +1769,10 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1789,10 +1789,10 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1809,10 +1809,10 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1829,10 +1829,10 @@
         <v>1</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1849,10 +1849,10 @@
         <v>1</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1869,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1889,10 +1889,10 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -1909,10 +1909,10 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1929,10 +1929,10 @@
         <v>1</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1949,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1989,10 +1989,10 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2009,10 +2009,10 @@
         <v>1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2029,10 +2029,10 @@
         <v>1</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2049,10 +2049,10 @@
         <v>1</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2069,10 +2069,10 @@
         <v>1</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2089,10 +2089,10 @@
         <v>1</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2109,10 +2109,10 @@
         <v>1</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -2129,10 +2129,10 @@
         <v>1</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2149,10 +2149,10 @@
         <v>1</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2169,10 +2169,10 @@
         <v>1</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -2189,10 +2189,10 @@
         <v>1</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>1</v>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C365DB93-DF27-499D-8C0D-CDA9EB9E9A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93173C1E-045F-48D1-AAB6-F20459508EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="49">
   <si>
     <t>uid</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>Storage_H2</t>
+  </si>
+  <si>
+    <t>HBfeed_mixer</t>
+  </si>
+  <si>
+    <t>ASU</t>
   </si>
 </sst>
 </file>
@@ -502,13 +508,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,8 +533,14 @@
       <c r="F1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -547,8 +559,14 @@
       <c r="F2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -567,8 +585,14 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -587,8 +611,14 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -607,8 +637,14 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -627,8 +663,14 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -647,8 +689,14 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -667,8 +715,14 @@
       <c r="F8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -687,8 +741,14 @@
       <c r="F9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -707,8 +767,14 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -727,8 +793,14 @@
       <c r="F11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -747,8 +819,14 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -767,8 +845,14 @@
       <c r="F13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -787,8 +871,14 @@
       <c r="F14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -807,8 +897,14 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -827,8 +923,14 @@
       <c r="F16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -847,8 +949,14 @@
       <c r="F17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -867,8 +975,14 @@
       <c r="F18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -887,8 +1001,14 @@
       <c r="F19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -907,8 +1027,14 @@
       <c r="F20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -927,8 +1053,14 @@
       <c r="F21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -947,8 +1079,14 @@
       <c r="F22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -967,8 +1105,14 @@
       <c r="F23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -987,8 +1131,14 @@
       <c r="F24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -1007,8 +1157,14 @@
       <c r="F25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1027,8 +1183,14 @@
       <c r="F26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1047,8 +1209,14 @@
       <c r="F27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1067,8 +1235,14 @@
       <c r="F28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1087,8 +1261,14 @@
       <c r="F29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1107,8 +1287,14 @@
       <c r="F30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1127,8 +1313,14 @@
       <c r="F31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -1147,8 +1339,14 @@
       <c r="F32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -1167,8 +1365,14 @@
       <c r="F33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -1187,8 +1391,14 @@
       <c r="F34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -1207,8 +1417,14 @@
       <c r="F35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -1227,8 +1443,14 @@
       <c r="F36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1247,8 +1469,14 @@
       <c r="F37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -1267,8 +1495,14 @@
       <c r="F38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1287,8 +1521,14 @@
       <c r="F39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1307,8 +1547,14 @@
       <c r="F40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -1327,8 +1573,14 @@
       <c r="F41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -1345,6 +1597,12 @@
         <v>0</v>
       </c>
       <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
         <v>0</v>
       </c>
     </row>
@@ -1355,13 +1613,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B540E4-80A6-4ECE-BFA5-AFA6333038A2}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1380,8 +1638,14 @@
       <c r="F1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1392,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1400,8 +1664,14 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1412,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1420,8 +1690,14 @@
       <c r="F3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1432,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1440,8 +1716,14 @@
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1460,8 +1742,14 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -1472,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1480,8 +1768,14 @@
       <c r="F6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -1492,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1500,8 +1794,14 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1512,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1520,8 +1820,14 @@
       <c r="F8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -1532,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1540,8 +1846,14 @@
       <c r="F9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1552,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1560,8 +1872,14 @@
       <c r="F10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1572,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1580,8 +1898,14 @@
       <c r="F11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -1592,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1600,8 +1924,14 @@
       <c r="F12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -1612,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -1620,8 +1950,14 @@
       <c r="F13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -1632,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1640,8 +1976,14 @@
       <c r="F14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1652,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1660,8 +2002,14 @@
       <c r="F15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -1672,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1680,8 +2028,14 @@
       <c r="F16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1692,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1700,8 +2054,14 @@
       <c r="F17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1712,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -1720,8 +2080,14 @@
       <c r="F18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -1732,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1740,8 +2106,14 @@
       <c r="F19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1752,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1760,8 +2132,14 @@
       <c r="F20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -1772,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1780,8 +2158,14 @@
       <c r="F21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -1792,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1800,8 +2184,14 @@
       <c r="F22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1812,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1820,8 +2210,14 @@
       <c r="F23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1832,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1840,8 +2236,14 @@
       <c r="F24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -1852,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1860,8 +2262,14 @@
       <c r="F25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1872,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1880,8 +2288,14 @@
       <c r="F26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1892,7 +2306,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -1900,8 +2314,14 @@
       <c r="F27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1912,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1920,8 +2340,14 @@
       <c r="F28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1932,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1940,8 +2366,14 @@
       <c r="F29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1952,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -1960,8 +2392,14 @@
       <c r="F30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1972,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1980,8 +2418,14 @@
       <c r="F31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -1992,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2000,8 +2444,14 @@
       <c r="F32">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -2012,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2020,8 +2470,14 @@
       <c r="F33">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -2032,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2040,8 +2496,14 @@
       <c r="F34">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -2052,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -2060,8 +2522,14 @@
       <c r="F35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -2072,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -2080,8 +2548,14 @@
       <c r="F36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -2092,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -2100,8 +2574,14 @@
       <c r="F37">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -2112,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -2120,8 +2600,14 @@
       <c r="F38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -2132,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -2140,8 +2626,14 @@
       <c r="F39">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -2160,8 +2652,14 @@
       <c r="F40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -2172,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -2180,8 +2678,14 @@
       <c r="F41">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -2192,12 +2696,18 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DB333F-14F7-4F07-B2ED-7EC0F5FEF452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61127FF6-9ECE-4E7F-AEEC-00A9FEF737BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -611,25 +611,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -637,25 +637,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -663,25 +663,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -689,25 +689,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -715,25 +715,25 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -741,25 +741,25 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61127FF6-9ECE-4E7F-AEEC-00A9FEF737BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC04F29-0957-49DC-B393-32B28B24BDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>cluster</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>NL3</t>
+  </si>
+  <si>
+    <t>SteamReformer</t>
   </si>
 </sst>
 </file>
@@ -385,10 +388,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -413,8 +416,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -439,8 +445,11 @@
       <c r="H2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -465,8 +474,11 @@
       <c r="H3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -491,8 +503,11 @@
       <c r="H4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -517,8 +532,11 @@
       <c r="H5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -543,8 +561,11 @@
       <c r="H6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -567,6 +588,9 @@
         <v>0</v>
       </c>
       <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
     </row>
@@ -577,10 +601,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,8 +629,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -631,8 +658,11 @@
       <c r="H2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -657,8 +687,11 @@
       <c r="H3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -683,8 +716,11 @@
       <c r="H4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -709,8 +745,11 @@
       <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -735,8 +774,11 @@
       <c r="H6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -760,6 +802,9 @@
       </c>
       <c r="H7">
         <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC04F29-0957-49DC-B393-32B28B24BDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741D8BC0-9BAF-4CEA-BA7A-CC861D9399B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -656,7 +656,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -714,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -731,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -760,7 +760,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741D8BC0-9BAF-4CEA-BA7A-CC861D9399B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCA93AE-D004-4FA2-B5B5-358233CBF60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -656,10 +656,10 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -685,10 +685,10 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -702,7 +702,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -731,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -743,10 +743,10 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -760,7 +760,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -772,10 +772,10 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -789,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -801,10 +801,10 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCA93AE-D004-4FA2-B5B5-358233CBF60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA94808E-5A38-426B-A7EA-04BD25A69261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11760" yWindow="12864" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -389,9 +389,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -449,7 +449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -478,7 +478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -507,7 +507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -536,7 +536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -602,9 +602,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -633,12 +633,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -662,12 +662,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -691,12 +691,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -720,12 +720,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -749,12 +749,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -778,12 +778,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>1</v>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA94808E-5A38-426B-A7EA-04BD25A69261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581541E2-426F-4490-ACA2-2198FA5772F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581541E2-426F-4490-ACA2-2198FA5772F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66065861-5711-4922-BB81-9F5347B36714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
   <si>
     <t>cluster</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>SteamReformer</t>
+  </si>
+  <si>
+    <t>Boiler_El</t>
   </si>
 </sst>
 </file>
@@ -389,9 +392,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +423,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -449,7 +452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -478,7 +481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -507,7 +510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -536,7 +539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -565,7 +568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -601,10 +604,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -632,8 +635,11 @@
       <c r="I1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -661,8 +667,11 @@
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -690,8 +699,11 @@
       <c r="I3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -719,8 +731,11 @@
       <c r="I4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -748,8 +763,11 @@
       <c r="I5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -777,8 +795,11 @@
       <c r="I6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -804,6 +825,9 @@
         <v>1</v>
       </c>
       <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66065861-5711-4922-BB81-9F5347B36714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5440C3-F001-405D-BE9E-DEE5FACE5C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5440C3-F001-405D-BE9E-DEE5FACE5C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E42423-B79B-4E49-A592-6ACDA77F1A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>cluster</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Boiler_El</t>
+  </si>
+  <si>
+    <t>eSMR_H2</t>
   </si>
 </sst>
 </file>
@@ -391,10 +394,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -422,8 +425,14 @@
       <c r="I1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -451,8 +460,14 @@
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -480,8 +495,14 @@
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -509,8 +530,14 @@
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -538,8 +565,14 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -567,8 +600,14 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -594,6 +633,12 @@
         <v>0</v>
       </c>
       <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>0</v>
       </c>
     </row>
@@ -604,10 +649,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -638,13 +683,16 @@
       <c r="J1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -670,13 +718,16 @@
       <c r="J2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -702,13 +753,16 @@
       <c r="J3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -734,13 +788,16 @@
       <c r="J4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -766,13 +823,16 @@
       <c r="J5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -798,13 +858,16 @@
       <c r="J6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -828,6 +891,9 @@
         <v>1</v>
       </c>
       <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E42423-B79B-4E49-A592-6ACDA77F1A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C71F52-129D-48A2-848D-0D688EDB0851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>cluster</t>
   </si>
@@ -77,6 +77,18 @@
   </si>
   <si>
     <t>eSMR_H2</t>
+  </si>
+  <si>
+    <t>CrackerFurnace</t>
+  </si>
+  <si>
+    <t>OlefinSeparation</t>
+  </si>
+  <si>
+    <t>eCrackerFurnace</t>
+  </si>
+  <si>
+    <t>eSMR_syngas</t>
   </si>
 </sst>
 </file>
@@ -394,10 +406,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -431,8 +443,20 @@
       <c r="K1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -466,8 +490,20 @@
       <c r="K2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -501,8 +537,20 @@
       <c r="K3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -536,8 +584,20 @@
       <c r="K4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -571,8 +631,20 @@
       <c r="K5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -606,8 +678,20 @@
       <c r="K6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -639,6 +723,18 @@
         <v>0</v>
       </c>
       <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
         <v>0</v>
       </c>
     </row>
@@ -649,10 +745,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,8 +782,20 @@
       <c r="K1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -721,8 +829,20 @@
       <c r="K2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -756,8 +876,20 @@
       <c r="K3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -791,8 +923,20 @@
       <c r="K4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -826,8 +970,20 @@
       <c r="K5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -861,8 +1017,20 @@
       <c r="K6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -894,6 +1062,18 @@
         <v>1</v>
       </c>
       <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C71F52-129D-48A2-848D-0D688EDB0851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01978A9-E3C4-423C-80EF-65A9CB0AEF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
   <si>
     <t>cluster</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>eSMR_syngas</t>
+  </si>
+  <si>
+    <t>MeOHsynthesis</t>
   </si>
 </sst>
 </file>
@@ -406,10 +409,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,8 +458,11 @@
       <c r="O1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -502,8 +508,11 @@
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -549,8 +558,11 @@
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -596,8 +608,11 @@
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -643,8 +658,11 @@
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -690,8 +708,11 @@
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -736,6 +757,9 @@
       </c>
       <c r="O7">
         <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -745,10 +769,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -794,286 +818,307 @@
       <c r="O1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01978A9-E3C4-423C-80EF-65A9CB0AEF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC964FA-53A5-4718-B45E-667368E80288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>cluster</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>MeOHsynthesis</t>
+  </si>
+  <si>
+    <t>MethanolToOlefins</t>
+  </si>
+  <si>
+    <t>rWGS</t>
+  </si>
+  <si>
+    <t>Plastic2methanol</t>
   </si>
 </sst>
 </file>
@@ -409,10 +418,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,8 +470,17 @@
       <c r="P1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -509,10 +527,19 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -559,10 +586,19 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -609,10 +645,19 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -659,10 +704,19 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -709,10 +763,19 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -759,7 +822,16 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -769,10 +841,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -821,304 +893,367 @@
       <c r="P1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC964FA-53A5-4718-B45E-667368E80288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEBF527-96C5-4EC7-BF1F-B8503AE5B1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -994,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -1053,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -1171,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1230,7 +1230,7 @@
         <v>1</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>1</v>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEBF527-96C5-4EC7-BF1F-B8503AE5B1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44092D8F-FB61-41DF-846F-8403FC04509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
   <si>
     <t>cluster</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Plastic2methanol</t>
+  </si>
+  <si>
+    <t>ethanolDH</t>
   </si>
 </sst>
 </file>
@@ -418,10 +421,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,8 +482,11 @@
       <c r="S1" t="s">
         <v>24</v>
       </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -538,8 +544,11 @@
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -597,8 +606,11 @@
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -656,8 +668,11 @@
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -715,8 +730,11 @@
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -774,8 +792,11 @@
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -831,6 +852,9 @@
         <v>0</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>0</v>
       </c>
     </row>
@@ -841,10 +865,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -902,34 +926,37 @@
       <c r="S1" t="s">
         <v>24</v>
       </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -938,57 +965,60 @@
         <v>0</v>
       </c>
       <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <v>1</v>
       </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -997,57 +1027,60 @@
         <v>0</v>
       </c>
       <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
         <v>1</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1056,57 +1089,60 @@
         <v>0</v>
       </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
         <v>1</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1115,57 +1151,60 @@
         <v>0</v>
       </c>
       <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1174,57 +1213,60 @@
         <v>0</v>
       </c>
       <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1233,27 +1275,30 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44092D8F-FB61-41DF-846F-8403FC04509E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ADF3C3-D111-433F-8B81-6B6AD1E5BB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4020" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>cluster</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Boiler_El</t>
   </si>
   <si>
-    <t>eSMR_H2</t>
-  </si>
-  <si>
     <t>CrackerFurnace</t>
   </si>
   <si>
@@ -104,6 +101,12 @@
   </si>
   <si>
     <t>ethanolDH</t>
+  </si>
+  <si>
+    <t>propaneDH</t>
+  </si>
+  <si>
+    <t>WGS_syngas</t>
   </si>
 </sst>
 </file>
@@ -421,10 +424,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,37 +459,40 @@
         <v>15</v>
       </c>
       <c r="K1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -547,8 +553,11 @@
       <c r="T2">
         <v>0</v>
       </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -609,8 +618,11 @@
       <c r="T3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -671,8 +683,11 @@
       <c r="T4">
         <v>0</v>
       </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -733,8 +748,11 @@
       <c r="T5">
         <v>0</v>
       </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -795,8 +813,11 @@
       <c r="T6">
         <v>0</v>
       </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -855,6 +876,9 @@
         <v>0</v>
       </c>
       <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
         <v>0</v>
       </c>
     </row>
@@ -865,10 +889,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -900,405 +924,426 @@
         <v>15</v>
       </c>
       <c r="K1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>22</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>24</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ADF3C3-D111-433F-8B81-6B6AD1E5BB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04977281-1E61-438D-A525-1E964F7F9B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4020" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04977281-1E61-438D-A525-1E964F7F9B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C7716E-5EC1-47D1-B930-E672E4935C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>cluster</t>
   </si>
@@ -98,12 +98,6 @@
   </si>
   <si>
     <t>Plastic2methanol</t>
-  </si>
-  <si>
-    <t>ethanolDH</t>
-  </si>
-  <si>
-    <t>propaneDH</t>
   </si>
   <si>
     <t>WGS_syngas</t>
@@ -424,10 +418,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,7 +453,7 @@
         <v>15</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L1" t="s">
         <v>19</v>
@@ -485,14 +479,8 @@
       <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -550,14 +538,8 @@
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -615,14 +597,8 @@
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -680,14 +656,8 @@
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -745,14 +715,8 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -810,14 +774,8 @@
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -873,12 +831,6 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
         <v>0</v>
       </c>
     </row>
@@ -889,10 +841,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -924,7 +876,7 @@
         <v>15</v>
       </c>
       <c r="K1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L1" t="s">
         <v>19</v>
@@ -950,14 +902,8 @@
       <c r="S1" t="s">
         <v>23</v>
       </c>
-      <c r="T1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1015,14 +961,8 @@
       <c r="S2">
         <v>1</v>
       </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1080,14 +1020,8 @@
       <c r="S3">
         <v>1</v>
       </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1145,14 +1079,8 @@
       <c r="S4">
         <v>1</v>
       </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1210,14 +1138,8 @@
       <c r="S5">
         <v>1</v>
       </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1275,14 +1197,8 @@
       <c r="S6">
         <v>1</v>
       </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1338,12 +1254,6 @@
         <v>1</v>
       </c>
       <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B80DBD-2C89-47F1-B8E8-FF3B3FDA14D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26B9374-725F-4248-A972-565DCAACFFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
   <si>
     <t>cluster</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>WGS_syngas</t>
+  </si>
+  <si>
+    <t>feedgas_mixer</t>
   </si>
 </sst>
 </file>
@@ -415,10 +418,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,8 +476,11 @@
       <c r="R1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -529,8 +535,11 @@
       <c r="R2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -585,8 +594,11 @@
       <c r="R3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -641,8 +653,11 @@
       <c r="R4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -697,8 +712,11 @@
       <c r="R5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -753,8 +771,11 @@
       <c r="R6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -807,6 +828,9 @@
         <v>0</v>
       </c>
       <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>0</v>
       </c>
     </row>
@@ -817,10 +841,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -875,8 +899,11 @@
       <c r="R1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -931,8 +958,11 @@
       <c r="R2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1017,11 @@
       <c r="R3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1076,11 @@
       <c r="R4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1099,8 +1135,11 @@
       <c r="R5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1194,11 @@
       <c r="R6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1209,6 +1251,9 @@
         <v>1</v>
       </c>
       <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26B9374-725F-4248-A972-565DCAACFFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50A538A-E120-4B4B-B7DF-F19B0BC189FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
   <si>
     <t>cluster</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>feedgas_mixer</t>
+  </si>
+  <si>
+    <t>HBfeed_splitter</t>
   </si>
 </sst>
 </file>
@@ -418,10 +421,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,8 +482,11 @@
       <c r="S1" t="s">
         <v>24</v>
       </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -538,8 +544,11 @@
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -597,8 +606,11 @@
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -656,8 +668,11 @@
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -715,8 +730,11 @@
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -774,8 +792,11 @@
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -831,6 +852,9 @@
         <v>0</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>0</v>
       </c>
     </row>
@@ -841,10 +865,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -902,8 +926,11 @@
       <c r="S1" t="s">
         <v>24</v>
       </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -961,8 +988,11 @@
       <c r="S2">
         <v>1</v>
       </c>
+      <c r="T2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1020,8 +1050,11 @@
       <c r="S3">
         <v>1</v>
       </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1079,8 +1112,11 @@
       <c r="S4">
         <v>1</v>
       </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1138,8 +1174,11 @@
       <c r="S5">
         <v>1</v>
       </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1197,8 +1236,11 @@
       <c r="S6">
         <v>1</v>
       </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1254,6 +1296,9 @@
         <v>1</v>
       </c>
       <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
         <v>1</v>
       </c>
     </row>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50A538A-E120-4B4B-B7DF-F19B0BC189FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB88E2E7-190B-45FF-A723-BA443CAF710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/plants_data/technologies.xlsx
+++ b/plants_data/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB88E2E7-190B-45FF-A723-BA443CAF710A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58E79FF-2BA3-4542-B119-95892CB45440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
   <si>
     <t>cluster</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>HBfeed_splitter</t>
+  </si>
+  <si>
+    <t>NL4</t>
   </si>
 </sst>
 </file>
@@ -421,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -855,6 +858,68 @@
         <v>0</v>
       </c>
       <c r="T7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
         <v>0</v>
       </c>
     </row>
@@ -865,7 +930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -1302,6 +1367,68 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
